--- a/Paket_6_Matematika_TKA_SD.xlsx
+++ b/Paket_6_Matematika_TKA_SD.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paket 6 Matematika" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -471,27 +471,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 1: contoh soal numerasi sederhana.</t>
+          <t>Sebuah distributor sembako memiliki stok awal 85 karung beras. Setiap karung memiliki berat 25 kg. Hari ini distributor menerima pasokan tambahan sebanyak 40 karung beras dengan berat yang sama. Jika 65 karung beras langsung didistribusikan ke pasar rakyat, berapa kilogram beras yang masih tersisa di gudang distributor?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 1.250 kg</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 1.500 kg</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 1.750 kg</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 2.000 kg</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -502,7 +502,11 @@
       <c r="H2" t="n">
         <v>60</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,27 +516,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 2: contoh soal numerasi sederhana.</t>
+          <t>Suhu udara di dalam lemari pembeku (freezer) mula-mula tercatat -12°C. Saat terjadi gangguan listrik, suhu di dalam freezer naik rata-rata 2°C setiap 10 menit. Setelah listrik padam selama 50 menit, petugas menyalakan generator darurat yang mampu menurunkan suhu 3°C dalam 5 menit pertama. Berapakah suhu akhir di dalam freezer?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. -5°C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. -2°C</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 1°C</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. -8°C</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -543,7 +547,11 @@
       <c r="H3" t="n">
         <v>60</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -553,27 +561,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 3: contoh soal numerasi sederhana.</t>
+          <t>Pak Danu memiliki kebun seluas 4 1/2 hektare. Sebanyak 1 3/4 hektare ditanami kelapa sawit, 1 1/2 hektare ditanami jagung hibrida, dan sisanya ditanami aneka sayuran hortikultura. Berapa hektare luas lahan kebun yang ditanami sayuran?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 1 1/4 hektare</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 1 1/2 hektare</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 1 3/8 hektare</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 1 3/4 hektare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -584,7 +592,11 @@
       <c r="H4" t="n">
         <v>60</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -594,27 +606,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 4: contoh soal numerasi sederhana.</t>
+          <t>Di stasiun kota, Kereta Api Logawa berangkat setiap 45 menit sekali, sedangkan Kereta Api Sancaka berangkat setiap 60 menit sekali. Jika kedua kereta api tersebut berangkat bersamaan pertama kali pada pukul 06.15, pada pukul berapa kedua kereta api tersebut akan berangkat bersamaan untuk kedua kalinya?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. Pukul 08.15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. Pukul 09.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. Pukul 09.45</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. Pukul 10.15</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -625,17 +637,21 @@
       <c r="H5" t="n">
         <v>60</v>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 5: contoh soal numerasi sederhana.</t>
+          <t>Sebuah sanggar seni menerima donasi 48 set kuas lukis, 72 buku sketsa, dan 96 tabung cat akrilik. Seluruh barang donasi tersebut akan dikemas ke dalam beberapa tas paket seni dengan komposisi isi yang sama banyak tanpa ada barang tersisa. Manakah pernyataan berikut yang BENAR? (Jawaban benar lebih dari satu) ☐ A. Jumlah paket seni terbanyak yang dapat dibentuk adalah 24 tas paket ☐ B. Setiap tas paket seni berisi 2 set kuas lukis dan 3 buku sketsa ☐ C. Setiap tas paket seni berisi 5 tabung cat akrilik ☐ D. Total seluruh perlengkapan seni di dalam setiap tas paket berjumlah 9 barang [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -666,7 +682,11 @@
       <c r="H6" t="n">
         <v>60</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -676,27 +696,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 6: contoh soal numerasi sederhana.</t>
+          <t>Pada sebuah denah perumahan, sebidang tanah lapangan fasilitas umum digambar dengan skala 1 : 400. Lapangan tersebut berbentuk persegi panjang dengan ukuran panjang 15 cm dan lebar 10 cm pada denah. Berapakah luas sebenarnya dari lapangan perumahan tersebut?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 1.200 m²</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 1.800 m²</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 2.400 m²</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 3.600 m²</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -707,17 +727,21 @@
       <c r="H7" t="n">
         <v>60</v>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 7: contoh soal numerasi sederhana.</t>
+          <t>Menjelang tahun ajaran baru, Toko Buku Cendekia memberikan promo potongan harga khusus untuk perlengkapan sekolah: • Paket A (Tas Sekolah): Harga label Rp150.000, diskon 20% • Paket B (Sepatu Sekolah): Harga label Rp200.000, diskon 15% • Paket C (Buku Tulis 1 Pak): Harga label Rp50.000, diskon 10% Berdasarkan data harga dan diskon tersebut, tentukan kebenaran dari pernyataan-pernyataan berikut! [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -748,7 +772,11 @@
       <c r="H8" t="n">
         <v>60</v>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -758,27 +786,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 8: contoh soal numerasi sederhana.</t>
+          <t>Seorang atlet renang berlatih dalam tiga sesi catatan waktu: sesi pertama 1 jam 15 menit 40 detik, sesi kedua 55 menit 35 detik, dan sesi ketiga 48 menit 25 detik. Berapa total waktu latihan atlet tersebut?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 2 jam 59 menit 40 detik</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 3 jam 00 menit 40 detik</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 3 jam 09 menit 40 detik</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 3 jam 15 menit 20 detik</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -789,7 +817,11 @@
       <c r="H9" t="n">
         <v>60</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -799,27 +831,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 9: contoh soal numerasi sederhana.</t>
+          <t>Pak Rahmat mengendarai mobil dari kota X ke kota Y yang berjarak 180 km dengan kecepatan rata-rata 60 km/jam. Di tengah perjalanan, beliau beristirahat di rest area selama 30 menit. Jika Pak Rahmat berangkat dari kota X pada pukul 07.45 WIB, pada pukul berapakah beliau tiba di kota Y?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 10.45 WIB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 11.15 WIB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 11.30 WIB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 11.45 WIB</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -830,7 +862,11 @@
       <c r="H10" t="n">
         <v>60</v>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -840,27 +876,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 10: contoh soal numerasi sederhana.</t>
+          <t>Sebuah truk pengangkut memuat 2,5 ton jagung pipil, 18 kuintal kedelai, dan 750 kg kacang tanah. Setelah dibongkar di gudang pabrik pakan ternak sebanyak 3.850 kg, berapa kilogram sisa muatan yang masih berada di atas bak truk?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 1.150 kg</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 1.200 kg</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 1.350 kg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 1.400 kg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -871,7 +907,11 @@
       <c r="H11" t="n">
         <v>60</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -881,27 +921,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 11: contoh soal numerasi sederhana.</t>
+          <t>Sebuah bak penampungan air berkapasitas 1.800 liter dalam keadaan kosong dialiri air melalui dua pipa kran sekaligus. Pipa kran A memiliki debit 25 liter/menit, sedangkan pipa kran B memiliki debit 20 liter/menit. Berapa menit waktu yang diperlukan agar bak penampungan tersebut terisi penuh?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 35 menit</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 40 menit</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 45 menit</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 50 menit</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -912,17 +952,21 @@
       <c r="H12" t="n">
         <v>60</v>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 12: contoh soal numerasi sederhana.</t>
+          <t>Perhatikan ciri-ciri bangun datar berikut: • Memiliki empat sisi dengan sepasang sisi sejajar yang tidak sama panjang • Memiliki dua sudut siku-siku • Kedua diagonalnya saling berpotongan tetapi tidak sama panjang dan tidak saling tegak lurus Manakah pernyataan yang BENAR mengenai bangun datar tersebut? (Jawaban benar lebih dari satu) ☐ A. Bangun datar tersebut adalah trapesium siku-siku ☐ B. Jumlah seluruh sudut dalamnya adalah 360° ☐ C. Bangun tersebut memiliki dua sumbu simetri lipat ☐ D. Tinggi trapesium sama dengan panjang salah satu sisi tegaknya yang membentuk sudut 90° [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -953,7 +997,11 @@
       <c r="H13" t="n">
         <v>60</v>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -963,27 +1011,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 13: contoh soal numerasi sederhana.</t>
+          <t>Sebuah taman rekreasi kota memiliki lintasan jogging berbentuk lingkaran dengan diameter 56 meter. Di sepanjang tepian luar lintasan akan ditanami pohon cemara perindang dengan jarak antar-pohon 4 meter. Berapa batang pohon cemara yang diperlukan di sekeliling lintasan tersebut? (Gunakan π = 22/7)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 40 pohon</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 44 pohon</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 48 pohon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 52 pohon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -994,7 +1042,11 @@
       <c r="H14" t="n">
         <v>60</v>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1004,27 +1056,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 14: contoh soal numerasi sederhana.</t>
+          <t>Sebuah wadah kado berbentuk kubus tanpa tutup memiliki panjang rusuk 25 cm. Bagian luar seluruh sisi tegak dan alas kotak tersebut akan dilapisi kertas kado bermotif batik. Berapakah luas minimal kertas kado yang dibutuhkan untuk membungkus kotak tersebut?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 2.500 cm²</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 3.125 cm²</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 3.750 cm²</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 4.250 cm²</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1035,17 +1087,21 @@
       <c r="H15" t="n">
         <v>60</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 15: contoh soal numerasi sederhana.</t>
+          <t>Sebuah tangki penampungan minyak berbentuk tabung memiliki jari-jari alas 70 cm dan tinggi 1,5 meter (150 cm). Tangki tersebut saat ini terisi minyak sebanyak separuh (1/2) dari kapasitas tampung totalnya. (Gunakan nilai π = 22/7). Tentukan kebenaran dari pernyataan-pernyataan berikut! [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1076,7 +1132,11 @@
       <c r="H16" t="n">
         <v>60</v>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1086,27 +1146,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 16: contoh soal numerasi sederhana.</t>
+          <t>Data penjualan seragam olahraga di koperasi sekolah selama lima hari tercatat sebagai berikut: Senin terjual 24 stel, Selasa 30 stel, Rabu 18 stel, Kamis 26 stel, dan Jumat 32 stel. Berapakah rata-rata (mean) penjualan seragam olahraga per hari di koperasi tersebut?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 24 stel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 26 stel</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 28 stel</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 30 stel</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1117,7 +1177,11 @@
       <c r="H17" t="n">
         <v>60</v>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1127,27 +1191,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 17: contoh soal numerasi sederhana.</t>
+          <t>Nilai ulangan harian matematika dari 12 siswa kelas VI adalah sebagai berikut: 75, 80, 85, 70, 80, 90, 85, 80, 75, 80, 95, 70. Tentukan nilai modus dan median dari data ulangan matematika tersebut berturut-turut!</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. Modus = 80 dan Median = 80</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. Modus = 80 dan Median = 82,5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. Modus = 85 dan Median = 80</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. Modus = 80 dan Median = 77,5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1158,17 +1222,21 @@
       <c r="H18" t="n">
         <v>60</v>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 18: contoh soal numerasi sederhana.</t>
+          <t>Sebuah sekolah dasar memiliki 180 siswa kelas VI yang mengikuti kegiatan ekstrakurikuler wajib dengan rincian persentase: • Pramuka = 40% • Dokter Kecil (PMR) = 25% • Robotik = 15% • Seni Tari = 20% Manakah pernyataan berikut yang BENAR mengenai data ekstrakurikuler tersebut? (Jawaban benar lebih dari satu) ☐ A. Jumlah siswa yang mengikuti ekstrakurikuler Pramuka adalah 72 anak ☐ B. Jumlah siswa yang mengikuti Dokter Kecil adalah 45 anak ☐ C. Selisih jumlah siswa peminat Pramuka dan Robotik adalah 40 anak ☐ D. Peminat Seni Tari berjumlah 36 anak [Pilihan Ganda Kompleks: Jawaban benar lebih dari satu]</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1199,7 +1267,11 @@
       <c r="H19" t="n">
         <v>60</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1209,27 +1281,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 19: contoh soal numerasi sederhana.</t>
+          <t>Pada bidang koordinat Kartesius, terdapat tiga titik sudut segitiga siku-siku yaitu titik K(-2, 1), titik L(4, 1), dan titik M(-2, 6). Jika satuan koordinat dihitung dalam sentimeter, berapakah luas segitiga KLM tersebut?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A. Pilihan A</t>
+          <t>A. 12 cm²</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>B. Pilihan B</t>
+          <t>B. 15 cm²</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>C. Pilihan C</t>
+          <t>C. 20 cm²</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>D. Pilihan D</t>
+          <t>D. 30 cm²</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1240,17 +1312,21 @@
       <c r="H20" t="n">
         <v>60</v>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Multiple</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[Paket 6] Soal Matematika 20: contoh soal numerasi sederhana.</t>
+          <t>Dalam sebuah kotak undian perayaan HUT Kemerdekaan RI di sekolah, terdapat 50 kupon bernomor 1 sampai dengan 50. Seorang siswa mengambil satu lembar kupon secara acak. Tentukan kebenaran dari pernyataan-pernyataan peluang berikut! [Pilihan Ganda Kompleks: Kategori Benar / Salah]</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1281,7 +1357,11 @@
       <c r="H21" t="n">
         <v>60</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Pembahasan lengkap tersedia di modul teks.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
